--- a/business_forms/038_data_handling_assessment--business_forms.xlsx
+++ b/business_forms/038_data_handling_assessment--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>data_disposal</t>
+          <t>data_disposal_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Data Disposal</t>
+          <t>Data Disposal 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>data_disposal_policies</t>
+          <t>data_disposal_policies_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Data Disposal Policies</t>
+          <t>Data Disposal Policies 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>data_disposal_procedures</t>
+          <t>data_disposal_procedures_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Data Disposal Procedures</t>
+          <t>Data Disposal Procedures 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>data_retention</t>
+          <t>data_retention_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Data Retention</t>
+          <t>Data Retention 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>access_to_data_subjects</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Access to Data Subjects</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>data_subject_right_choices</t>
+          <t>data_access_management_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>access_to_data_subjects</t>
+          <t>data_access_management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Access to Data Subjects</t>
+          <t>Data Access Management</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>data_access_management</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Data Access Management</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>data_access_management_choices</t>
+          <t>data_anonymization_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>data_access_management</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Data Access Management</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1692,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>data_anonymization_choices</t>
+          <t>data_pseudonymization_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1726,29 +1726,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>data_pseudonymization_choices</t>
+          <t>data_analytics_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1760,29 +1760,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>data_analytics_choices</t>
+          <t>data_ownership_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>data_ownership_choices</t>
+          <t>data_archiving_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1828,29 +1828,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>data_archiving_choices</t>
+          <t>data_backup_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1862,180 +1862,163 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>data_backup_choices</t>
+          <t>data_disposal_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>data_disposal_choices</t>
+          <t>data_disposal_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>data_disposal_choices</t>
+          <t>data_disposal_policies_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>secure_erasure</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Secure Erasure</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>data_disposal_policies_choices</t>
+          <t>data_disposal_policies_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>secure_erasure</t>
+          <t>destruction</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Secure Erasure</t>
+          <t>Destruction</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>data_disposal_policies_choices</t>
+          <t>data_disposal_policies_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>destruction</t>
+          <t>deletion</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Destruction</t>
+          <t>Deletion</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>data_disposal_policies_choices</t>
+          <t>data_disposal_procedures_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>deletion</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Deletion</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>data_disposal_procedures_choices</t>
+          <t>data_disposal_procedures_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>data_disposal_procedures_choices</t>
+          <t>data_retention_2_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>data_retention_choices</t>
+          <t>data_retention_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>data_retention_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
         <is>
           <t>False</t>
         </is>
